--- a/assessment_forms/046_medical_knowledge_assessment--assessment_forms.xlsx
+++ b/assessment_forms/046_medical_knowledge_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,478 +520,562 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>medical_knowledge_assessment</t>
+          <t>medical_knowledge</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medical Knowledge Assessment</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your current level of medical knowledge?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This question is to assess your current level of medical knowledge.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>section_a</t>
+          <t>medical_degree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Section A</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Medical Degree Earned</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>This question is to assess your highest level of medical degree earned.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>a_question_1</t>
+          <t>year_of_birth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is a question 1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Year of Birth</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>This question is to determine your birth year.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>a_question_2</t>
+          <t>medical_license_expiration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is a question 2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Medical License Expiration Date</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>This question is to determine your medical license expiration date.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>a_question_3</t>
+          <t>section_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is a question 3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Section A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Anatomy and Physiology</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>a_question_4</t>
+          <t>a_question_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is a question 4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Circulatory System Function</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What is the function of the circulatory system?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>b_question_1</t>
+          <t>a_question_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is b question 1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Cellular Respiration Process</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What is the process of cellular respiration?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>b_question_2</t>
+          <t>a_question_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is b question 2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Respiratory System Organs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>What are the main organs in the respiratory system?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>a_question_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Photosynthesis Process</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>What is the process of photosynthesis?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>time_of_birth</t>
+          <t>b_question_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Time of Birth</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Hypoglycemia Definition</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>What is the definition of hypoglycemia?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>b_question_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Type 2 Diabetes Treatment</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>What is the treatment for type 2 diabetes?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>b_question_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Hypertension Definition</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What is the definition of hypertension?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_school</t>
+          <t>b_question_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Medical School</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Pneumonia Treatment</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>What is the treatment for pneumonia?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>medical_license</t>
+          <t>c_question_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medical License</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Informed Consent Definition</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>What is the definition of informed consent?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medical_license_issue_date</t>
+          <t>c_question_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medical License Issue Date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Confidentiality Definition</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>What is the definition of confidentiality?</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical_license_expiration_date</t>
+          <t>c_question_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical License Expiration Date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Medical Malpractice Definition</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>What is the definition of medical malpractice?</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>section_b</t>
+          <t>c_question_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Section B</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Patient Autonomy Definition</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>What is the definition of patient autonomy?</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>c_question_1</t>
+          <t>medical_license</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is a question 1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Medical License</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>This question is to determine your medical license type.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>c_question_2</t>
+          <t>medical_residency</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What is a question 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Medical Residency</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>This question is to determine your medical residency type.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>c_question_3</t>
+          <t>medical_license_number</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is a question 3</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Medical License Number</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>This question is to determine your medical license number.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>medical_license_type</t>
+          <t>medical_license_status</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medical License Type</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Medical License Status</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>This question is to determine your medical license status.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1003,87 +1087,49 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>medical_license_number</t>
+          <t>medical_degree_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Medical License Number</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Medical Degree</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>This question is to determine your medical degree.</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>medical_license_status</t>
+          <t>section_c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Medical License Status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Section C</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Medical Ethics</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>medical_degree</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Medical Degree</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>medical_residency</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Medical Residency</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1144,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1194,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>lungs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Lungs</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>blood_vessels</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Blood Vessels</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>aerobic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Aerobic</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>anaerobic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Anaerobic</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>fermentation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Fermentation</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>lungs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Lungs</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>trachea</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Trachea</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>esophagus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Esophagus</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>light_dependent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Light dependent</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1347,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>light_independent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Light independent</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1364,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1381,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>low_blood_sugar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Low blood sugar</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1398,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>high_blood_sugar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>High blood sugar</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1415,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1432,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>insulin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Insulin</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1449,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Exercise</t>
         </is>
       </c>
     </row>
@@ -1420,214 +1466,367 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Diet</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>c_question_1_choices</t>
+          <t>b_question_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>High blood pressure</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>c_question_1_choices</t>
+          <t>b_question_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>low_blood_pressure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Low blood pressure</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>c_question_1_choices</t>
+          <t>b_question_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>normal_blood_pressure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Normal blood pressure</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>c_question_2_choices</t>
+          <t>b_question_4_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>antibiotics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Antibiotics</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>c_question_2_choices</t>
+          <t>b_question_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Rest</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>c_question_2_choices</t>
+          <t>b_question_4_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>fluids</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Fluids</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>c_question_3_choices</t>
+          <t>c_question_1_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>permission_given</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Permission given</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>c_question_3_choices</t>
+          <t>c_question_1_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>permission_not_given</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Permission not given</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>c_question_3_choices</t>
+          <t>c_question_1_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>medical_license_status_choices</t>
+          <t>c_question_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>patient_information_kept_secret</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Patient information kept secret</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>medical_license_status_choices</t>
+          <t>c_question_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>patient_information_shared</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Patient information shared</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>c_question_2_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>c_question_3_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>unprofessional_behavior</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Unprofessional behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>c_question_3_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>professional_behavior</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Professional behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>c_question_3_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>c_question_4_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>patient_decision_making_power</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Patient decision making power</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>c_question_4_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>doctor_decision_making_power</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Doctor decision making power</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>c_question_4_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>medical_license_status_choices</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>medical_license_status_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>medical_license_status_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Suspended</t>
         </is>
